--- a/tables/datas/common/#MapMonster-地图怪物表.xlsx
+++ b/tables/datas/common/#MapMonster-地图怪物表.xlsx
@@ -2,39 +2,373 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28800" windowHeight="11805" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="21">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -42,15 +376,305 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -122,6 +746,37 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>System</author>
+  </authors>
+  <commentList>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>怪物死亡后多久复活（秒）
+0 表示死亡后不再复活</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>复活类型（枚举）
+SpawnPoint = 在出生点复活
+DeathPoint = 在死亡位置复活
+RandomNearSpawn = 在出生点附近随机位置复活（范围由 respawn_range 决定）</t>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <t>复活随机范围（格子数）
+仅当 respawn_type = RandomNearSpawn 时生效
+范围包含出生点周围该半径内的所有可行走格子</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -403,7 +1058,6 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -413,8 +1067,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:K35"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
+  <cols>
+    <col width="12.5" customWidth="1" min="8" max="8"/>
+    <col width="11.875" customWidth="1" min="9" max="9"/>
+    <col width="20.25" customWidth="1" min="10" max="10"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -462,6 +1121,16 @@
           <t>ai_id</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>respawn_type</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>respawn_range</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -509,6 +1178,16 @@
           <t>int</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>common.ERespawnType</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -556,6 +1235,16 @@
           <t>s</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -565,7 +1254,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>配置ID</t>
+          <t>怪物ID</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -575,22 +1264,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>怪物ID</t>
+          <t>怪物配置ID</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>出生X</t>
+          <t>出生X坐标</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>出生Y</t>
+          <t>出生Y坐标</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>重生秒数</t>
+          <t>复活时间(秒)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -601,6 +1290,16 @@
       <c r="I4" t="inlineStr">
         <is>
           <t>AI配置ID</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>复活类型</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>复活随机范围(格子数)</t>
         </is>
       </c>
     </row>
@@ -629,6 +1328,14 @@
       <c r="I5" t="n">
         <v>2</v>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>SpawnPoint</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="n">
@@ -641,10 +1348,10 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6" t="n">
         <v>30</v>
@@ -654,6 +1361,14 @@
       </c>
       <c r="I6" t="n">
         <v>2</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>SpawnPoint</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -664,7 +1379,7 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>15</v>
@@ -673,13 +1388,21 @@
         <v>15</v>
       </c>
       <c r="G7" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
       </c>
       <c r="I7" t="n">
         <v>2</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>SpawnPoint</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -690,25 +1413,952 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>18</v>
+      </c>
+      <c r="F8" t="n">
+        <v>18</v>
+      </c>
+      <c r="G8" t="n">
+        <v>30</v>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>SpawnPoint</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>20</v>
+      </c>
+      <c r="F9" t="n">
+        <v>20</v>
+      </c>
+      <c r="G9" t="n">
+        <v>45</v>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>SpawnPoint</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>22</v>
+      </c>
+      <c r="F10" t="n">
+        <v>22</v>
+      </c>
+      <c r="G10" t="n">
+        <v>45</v>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>SpawnPoint</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>7</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
         <v>3</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E11" t="n">
+        <v>30</v>
+      </c>
+      <c r="F11" t="n">
+        <v>30</v>
+      </c>
+      <c r="G11" t="n">
+        <v>60</v>
+      </c>
+      <c r="H11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>SpawnPoint</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>8</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>32</v>
+      </c>
+      <c r="F12" t="n">
+        <v>32</v>
+      </c>
+      <c r="G12" t="n">
+        <v>60</v>
+      </c>
+      <c r="H12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>SpawnPoint</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>9</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" t="n">
+        <v>40</v>
+      </c>
+      <c r="F13" t="n">
+        <v>40</v>
+      </c>
+      <c r="G13" t="n">
+        <v>60</v>
+      </c>
+      <c r="H13" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>SpawnPoint</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>10</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" t="n">
+        <v>42</v>
+      </c>
+      <c r="F14" t="n">
+        <v>42</v>
+      </c>
+      <c r="G14" t="n">
+        <v>60</v>
+      </c>
+      <c r="H14" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>SpawnPoint</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>11</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" t="n">
+        <v>10</v>
+      </c>
+      <c r="G15" t="n">
+        <v>45</v>
+      </c>
+      <c r="H15" t="b">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>SpawnPoint</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>12</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>12</v>
+      </c>
+      <c r="F16" t="n">
+        <v>12</v>
+      </c>
+      <c r="G16" t="n">
+        <v>45</v>
+      </c>
+      <c r="H16" t="b">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>SpawnPoint</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>13</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" t="n">
+        <v>15</v>
+      </c>
+      <c r="F17" t="n">
+        <v>15</v>
+      </c>
+      <c r="G17" t="n">
+        <v>45</v>
+      </c>
+      <c r="H17" t="b">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>SpawnPoint</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>14</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E18" t="n">
         <v>20</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F18" t="n">
         <v>20</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G18" t="n">
         <v>60</v>
       </c>
-      <c r="H8" t="b">
-        <v>1</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2</v>
+      <c r="H18" t="b">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>SpawnPoint</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>15</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>6</v>
+      </c>
+      <c r="E19" t="n">
+        <v>22</v>
+      </c>
+      <c r="F19" t="n">
+        <v>22</v>
+      </c>
+      <c r="G19" t="n">
+        <v>60</v>
+      </c>
+      <c r="H19" t="b">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>SpawnPoint</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>16</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E20" t="n">
+        <v>25</v>
+      </c>
+      <c r="F20" t="n">
+        <v>25</v>
+      </c>
+      <c r="G20" t="n">
+        <v>60</v>
+      </c>
+      <c r="H20" t="b">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>SpawnPoint</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>17</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>7</v>
+      </c>
+      <c r="E21" t="n">
+        <v>30</v>
+      </c>
+      <c r="F21" t="n">
+        <v>30</v>
+      </c>
+      <c r="G21" t="n">
+        <v>75</v>
+      </c>
+      <c r="H21" t="b">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>SpawnPoint</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>18</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" t="n">
+        <v>7</v>
+      </c>
+      <c r="E22" t="n">
+        <v>32</v>
+      </c>
+      <c r="F22" t="n">
+        <v>32</v>
+      </c>
+      <c r="G22" t="n">
+        <v>75</v>
+      </c>
+      <c r="H22" t="b">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>SpawnPoint</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>19</v>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="n">
+        <v>7</v>
+      </c>
+      <c r="E23" t="n">
+        <v>35</v>
+      </c>
+      <c r="F23" t="n">
+        <v>35</v>
+      </c>
+      <c r="G23" t="n">
+        <v>75</v>
+      </c>
+      <c r="H23" t="b">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>SpawnPoint</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>20</v>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="n">
+        <v>7</v>
+      </c>
+      <c r="E24" t="n">
+        <v>38</v>
+      </c>
+      <c r="F24" t="n">
+        <v>38</v>
+      </c>
+      <c r="G24" t="n">
+        <v>75</v>
+      </c>
+      <c r="H24" t="b">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>SpawnPoint</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>21</v>
+      </c>
+      <c r="C25" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" t="n">
+        <v>8</v>
+      </c>
+      <c r="E25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G25" t="n">
+        <v>60</v>
+      </c>
+      <c r="H25" t="b">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>SpawnPoint</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>22</v>
+      </c>
+      <c r="C26" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" t="n">
+        <v>8</v>
+      </c>
+      <c r="E26" t="n">
+        <v>12</v>
+      </c>
+      <c r="F26" t="n">
+        <v>12</v>
+      </c>
+      <c r="G26" t="n">
+        <v>60</v>
+      </c>
+      <c r="H26" t="b">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>SpawnPoint</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>23</v>
+      </c>
+      <c r="C27" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" t="n">
+        <v>8</v>
+      </c>
+      <c r="E27" t="n">
+        <v>15</v>
+      </c>
+      <c r="F27" t="n">
+        <v>15</v>
+      </c>
+      <c r="G27" t="n">
+        <v>60</v>
+      </c>
+      <c r="H27" t="b">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>SpawnPoint</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>24</v>
+      </c>
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>9</v>
+      </c>
+      <c r="E28" t="n">
+        <v>20</v>
+      </c>
+      <c r="F28" t="n">
+        <v>20</v>
+      </c>
+      <c r="G28" t="n">
+        <v>75</v>
+      </c>
+      <c r="H28" t="b">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>4</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>SpawnPoint</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>25</v>
+      </c>
+      <c r="C29" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" t="n">
+        <v>9</v>
+      </c>
+      <c r="E29" t="n">
+        <v>22</v>
+      </c>
+      <c r="F29" t="n">
+        <v>22</v>
+      </c>
+      <c r="G29" t="n">
+        <v>75</v>
+      </c>
+      <c r="H29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>4</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>SpawnPoint</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>26</v>
+      </c>
+      <c r="C30" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" t="n">
+        <v>9</v>
+      </c>
+      <c r="E30" t="n">
+        <v>25</v>
+      </c>
+      <c r="F30" t="n">
+        <v>25</v>
+      </c>
+      <c r="G30" t="n">
+        <v>75</v>
+      </c>
+      <c r="H30" t="b">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>4</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>SpawnPoint</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>27</v>
+      </c>
+      <c r="C31" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="n">
+        <v>30</v>
+      </c>
+      <c r="F31" t="n">
+        <v>30</v>
+      </c>
+      <c r="G31" t="n">
+        <v>90</v>
+      </c>
+      <c r="H31" t="b">
+        <v>1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>5</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>SpawnPoint</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>28</v>
+      </c>
+      <c r="C32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="n">
+        <v>32</v>
+      </c>
+      <c r="F32" t="n">
+        <v>32</v>
+      </c>
+      <c r="G32" t="n">
+        <v>90</v>
+      </c>
+      <c r="H32" t="b">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>SpawnPoint</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>29</v>
+      </c>
+      <c r="C33" t="n">
+        <v>3</v>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="n">
+        <v>35</v>
+      </c>
+      <c r="F33" t="n">
+        <v>35</v>
+      </c>
+      <c r="G33" t="n">
+        <v>90</v>
+      </c>
+      <c r="H33" t="b">
+        <v>1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>5</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>SpawnPoint</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>30</v>
+      </c>
+      <c r="C34" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" t="n">
+        <v>11</v>
+      </c>
+      <c r="E34" t="n">
+        <v>40</v>
+      </c>
+      <c r="F34" t="n">
+        <v>40</v>
+      </c>
+      <c r="G34" t="n">
+        <v>120</v>
+      </c>
+      <c r="H34" t="b">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>5</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>SpawnPoint</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>31</v>
+      </c>
+      <c r="C35" t="n">
+        <v>3</v>
+      </c>
+      <c r="D35" t="n">
+        <v>11</v>
+      </c>
+      <c r="E35" t="n">
+        <v>42</v>
+      </c>
+      <c r="F35" t="n">
+        <v>42</v>
+      </c>
+      <c r="G35" t="n">
+        <v>120</v>
+      </c>
+      <c r="H35" t="b">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>5</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>SpawnPoint</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/tables/datas/common/#MapMonster-地图怪物表.xlsx
+++ b/tables/datas/common/#MapMonster-地图怪物表.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28800" windowHeight="11805" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1067,7 +1067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <cols>
     <col width="12.5" customWidth="1" min="8" max="8"/>
@@ -2357,6 +2357,108 @@
         <v>0</v>
       </c>
     </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>32</v>
+      </c>
+      <c r="C36" t="n">
+        <v>4</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2</v>
+      </c>
+      <c r="E36" t="n">
+        <v>55</v>
+      </c>
+      <c r="F36" t="n">
+        <v>50</v>
+      </c>
+      <c r="G36" t="n">
+        <v>30</v>
+      </c>
+      <c r="H36" t="b">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>2</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>SpawnPoint</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="n">
+        <v>33</v>
+      </c>
+      <c r="C37" t="n">
+        <v>4</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" t="n">
+        <v>50</v>
+      </c>
+      <c r="F37" t="n">
+        <v>55</v>
+      </c>
+      <c r="G37" t="n">
+        <v>30</v>
+      </c>
+      <c r="H37" t="b">
+        <v>1</v>
+      </c>
+      <c r="I37" t="n">
+        <v>2</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>SpawnPoint</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="n">
+        <v>34</v>
+      </c>
+      <c r="C38" t="n">
+        <v>4</v>
+      </c>
+      <c r="D38" t="n">
+        <v>2</v>
+      </c>
+      <c r="E38" t="n">
+        <v>45</v>
+      </c>
+      <c r="F38" t="n">
+        <v>50</v>
+      </c>
+      <c r="G38" t="n">
+        <v>30</v>
+      </c>
+      <c r="H38" t="b">
+        <v>1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>SpawnPoint</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>

--- a/tables/datas/common/#MapMonster-地图怪物表.xlsx
+++ b/tables/datas/common/#MapMonster-地图怪物表.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28800" windowHeight="11805" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1067,7 +1067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:K44"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <cols>
     <col width="12.5" customWidth="1" min="8" max="8"/>
@@ -1305,13 +1305,13 @@
     </row>
     <row r="5">
       <c r="B5" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
@@ -1320,7 +1320,7 @@
         <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
@@ -1339,13 +1339,13 @@
     </row>
     <row r="6">
       <c r="B6" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
         <v>12</v>
@@ -1354,7 +1354,7 @@
         <v>12</v>
       </c>
       <c r="G6" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
@@ -1373,13 +1373,13 @@
     </row>
     <row r="7">
       <c r="B7" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
         <v>15</v>
@@ -1388,7 +1388,7 @@
         <v>15</v>
       </c>
       <c r="G7" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
@@ -1407,22 +1407,22 @@
     </row>
     <row r="8">
       <c r="B8" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F8" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G8" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
@@ -1441,22 +1441,22 @@
     </row>
     <row r="9">
       <c r="B9" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F9" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G9" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
@@ -1475,22 +1475,22 @@
     </row>
     <row r="10">
       <c r="B10" t="n">
+        <v>16</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
         <v>6</v>
       </c>
-      <c r="C10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" t="n">
-        <v>2</v>
-      </c>
       <c r="E10" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F10" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G10" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
@@ -1509,13 +1509,13 @@
     </row>
     <row r="11">
       <c r="B11" t="n">
+        <v>17</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
         <v>7</v>
-      </c>
-      <c r="C11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" t="n">
-        <v>3</v>
       </c>
       <c r="E11" t="n">
         <v>30</v>
@@ -1524,7 +1524,7 @@
         <v>30</v>
       </c>
       <c r="G11" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
@@ -1543,13 +1543,13 @@
     </row>
     <row r="12">
       <c r="B12" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
         <v>32</v>
@@ -1558,7 +1558,7 @@
         <v>32</v>
       </c>
       <c r="G12" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
@@ -1577,28 +1577,28 @@
     </row>
     <row r="13">
       <c r="B13" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F13" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G13" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1611,28 +1611,28 @@
     </row>
     <row r="14">
       <c r="B14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F14" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G14" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1645,13 +1645,13 @@
     </row>
     <row r="15">
       <c r="B15" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
@@ -1660,7 +1660,7 @@
         <v>10</v>
       </c>
       <c r="G15" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
@@ -1679,13 +1679,13 @@
     </row>
     <row r="16">
       <c r="B16" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
         <v>12</v>
@@ -1694,7 +1694,7 @@
         <v>12</v>
       </c>
       <c r="G16" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
@@ -1713,13 +1713,13 @@
     </row>
     <row r="17">
       <c r="B17" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
         <v>15</v>
@@ -1728,7 +1728,7 @@
         <v>15</v>
       </c>
       <c r="G17" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
@@ -1747,13 +1747,13 @@
     </row>
     <row r="18">
       <c r="B18" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E18" t="n">
         <v>20</v>
@@ -1762,13 +1762,13 @@
         <v>20</v>
       </c>
       <c r="G18" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1781,13 +1781,13 @@
     </row>
     <row r="19">
       <c r="B19" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E19" t="n">
         <v>22</v>
@@ -1796,13 +1796,13 @@
         <v>22</v>
       </c>
       <c r="G19" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1815,13 +1815,13 @@
     </row>
     <row r="20">
       <c r="B20" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E20" t="n">
         <v>25</v>
@@ -1830,13 +1830,13 @@
         <v>25</v>
       </c>
       <c r="G20" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1849,13 +1849,13 @@
     </row>
     <row r="21">
       <c r="B21" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E21" t="n">
         <v>30</v>
@@ -1864,13 +1864,13 @@
         <v>30</v>
       </c>
       <c r="G21" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1883,13 +1883,13 @@
     </row>
     <row r="22">
       <c r="B22" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E22" t="n">
         <v>32</v>
@@ -1898,13 +1898,13 @@
         <v>32</v>
       </c>
       <c r="G22" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1917,13 +1917,13 @@
     </row>
     <row r="23">
       <c r="B23" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E23" t="n">
         <v>35</v>
@@ -1932,13 +1932,13 @@
         <v>35</v>
       </c>
       <c r="G23" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1951,28 +1951,28 @@
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E24" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F24" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G24" t="n">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1985,28 +1985,28 @@
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="C25" t="n">
         <v>3</v>
       </c>
       <c r="D25" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E25" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="F25" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="G25" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2019,22 +2019,22 @@
     </row>
     <row r="26">
       <c r="B26" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="F26" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="G26" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
@@ -2053,22 +2053,22 @@
     </row>
     <row r="27">
       <c r="B27" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="F27" t="n">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="G27" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
@@ -2087,28 +2087,28 @@
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="F28" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G28" t="n">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2121,28 +2121,28 @@
     </row>
     <row r="29">
       <c r="B29" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F29" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G29" t="n">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2150,33 +2150,33 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F30" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G30" t="n">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -2184,33 +2184,33 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F31" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="G31" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2218,33 +2218,33 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E32" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F32" t="n">
         <v>32</v>
       </c>
       <c r="G32" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2252,33 +2252,33 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E33" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="F33" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="G33" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2286,33 +2286,33 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="F34" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="G34" t="n">
-        <v>120</v>
+        <v>45</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2320,33 +2320,33 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E35" t="n">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="F35" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G35" t="n">
-        <v>120</v>
+        <v>45</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2354,27 +2354,27 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E36" t="n">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="F36" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="G36" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
@@ -2388,27 +2388,27 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="C37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="F37" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G37" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
@@ -2422,41 +2422,245 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="C38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E38" t="n">
+        <v>32</v>
+      </c>
+      <c r="F38" t="n">
+        <v>66</v>
+      </c>
+      <c r="G38" t="n">
         <v>45</v>
       </c>
-      <c r="F38" t="n">
+      <c r="H38" t="b">
+        <v>1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>SpawnPoint</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>45</v>
+      </c>
+      <c r="C39" t="n">
+        <v>5</v>
+      </c>
+      <c r="D39" t="n">
+        <v>3</v>
+      </c>
+      <c r="E39" t="n">
+        <v>62</v>
+      </c>
+      <c r="F39" t="n">
+        <v>64</v>
+      </c>
+      <c r="G39" t="n">
+        <v>45</v>
+      </c>
+      <c r="H39" t="b">
+        <v>1</v>
+      </c>
+      <c r="I39" t="n">
+        <v>2</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>SpawnPoint</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>46</v>
+      </c>
+      <c r="C40" t="n">
+        <v>5</v>
+      </c>
+      <c r="D40" t="n">
+        <v>3</v>
+      </c>
+      <c r="E40" t="n">
+        <v>56</v>
+      </c>
+      <c r="F40" t="n">
+        <v>56</v>
+      </c>
+      <c r="G40" t="n">
+        <v>45</v>
+      </c>
+      <c r="H40" t="b">
+        <v>1</v>
+      </c>
+      <c r="I40" t="n">
+        <v>2</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>SpawnPoint</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="n">
+        <v>47</v>
+      </c>
+      <c r="C41" t="n">
+        <v>5</v>
+      </c>
+      <c r="D41" t="n">
+        <v>12</v>
+      </c>
+      <c r="E41" t="n">
+        <v>36</v>
+      </c>
+      <c r="F41" t="n">
+        <v>10</v>
+      </c>
+      <c r="G41" t="n">
+        <v>120</v>
+      </c>
+      <c r="H41" t="b">
+        <v>1</v>
+      </c>
+      <c r="I41" t="n">
+        <v>2</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>SpawnPoint</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="n">
+        <v>48</v>
+      </c>
+      <c r="C42" t="n">
+        <v>5</v>
+      </c>
+      <c r="D42" t="n">
+        <v>12</v>
+      </c>
+      <c r="E42" t="n">
+        <v>44</v>
+      </c>
+      <c r="F42" t="n">
+        <v>12</v>
+      </c>
+      <c r="G42" t="n">
+        <v>120</v>
+      </c>
+      <c r="H42" t="b">
+        <v>1</v>
+      </c>
+      <c r="I42" t="n">
+        <v>2</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>SpawnPoint</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="n">
+        <v>49</v>
+      </c>
+      <c r="C43" t="n">
+        <v>5</v>
+      </c>
+      <c r="D43" t="n">
+        <v>12</v>
+      </c>
+      <c r="E43" t="n">
+        <v>48</v>
+      </c>
+      <c r="F43" t="n">
+        <v>8</v>
+      </c>
+      <c r="G43" t="n">
+        <v>120</v>
+      </c>
+      <c r="H43" t="b">
+        <v>1</v>
+      </c>
+      <c r="I43" t="n">
+        <v>2</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>SpawnPoint</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="n">
         <v>50</v>
       </c>
-      <c r="G38" t="n">
-        <v>30</v>
-      </c>
-      <c r="H38" t="b">
-        <v>1</v>
-      </c>
-      <c r="I38" t="n">
-        <v>2</v>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>SpawnPoint</t>
-        </is>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="C44" t="n">
+        <v>5</v>
+      </c>
+      <c r="D44" t="n">
+        <v>13</v>
+      </c>
+      <c r="E44" t="n">
+        <v>52</v>
+      </c>
+      <c r="F44" t="n">
+        <v>52</v>
+      </c>
+      <c r="G44" t="n">
+        <v>300</v>
+      </c>
+      <c r="H44" t="b">
+        <v>1</v>
+      </c>
+      <c r="I44" t="n">
+        <v>2</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>SpawnPoint</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
